--- a/internal_doc/14.性能分析/sdbimport/bulkinsert.xlsx
+++ b/internal_doc/14.性能分析/sdbimport/bulkinsert.xlsx
@@ -4,19 +4,19 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="bulkinsert_100" sheetId="1" r:id="rId1"/>
+    <sheet name="bulkinsert_1k" sheetId="2" r:id="rId2"/>
+    <sheet name="import_csv" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="26">
   <si>
     <t>插入100w记录</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -51,38 +51,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>92s</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>40s</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>19s</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>17s</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>80s</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>117s</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>insert.py</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>134s</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>AutoIndexId: false</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -92,6 +64,62 @@
   </si>
   <si>
     <t>2GB内存</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每条记录100字节</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每条记录1K字节</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>导入100w记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdbimport未改进</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>单位：秒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>csv格式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>standalone</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>coordinator</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>standalone</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>coordinator</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sharding</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4个数据节点，两个虚拟机，范围分区</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ShardingKey:{i:1}(i有序)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ShardingKey:{int:1}(int无序)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -123,7 +151,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -146,16 +174,36 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -452,32 +500,39 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B3:F10"/>
+  <dimension ref="A3:F10"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
+    <col min="1" max="1" width="13.25" customWidth="1"/>
     <col min="2" max="2" width="12.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:6">
+    <row r="3" spans="1:6">
       <c r="B3" t="s">
         <v>0</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="2:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="B4" t="s">
-        <v>14</v>
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
       </c>
       <c r="F4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="36.75" customHeight="1">
+      <c r="A6" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="6" spans="2:6" ht="36.75" customHeight="1">
       <c r="B6" s="1" t="s">
         <v>2</v>
       </c>
@@ -494,52 +549,55 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="2:6" ht="19.5" customHeight="1">
+    <row r="7" spans="1:6" ht="19.5" customHeight="1">
+      <c r="A7" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="B7" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="2:6" ht="22.5" customHeight="1">
+      <c r="C7" s="2">
+        <v>80</v>
+      </c>
+      <c r="D7" s="2">
+        <v>92</v>
+      </c>
+      <c r="E7" s="2">
+        <v>117</v>
+      </c>
+      <c r="F7" s="2">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="22.5" customHeight="1">
       <c r="B8" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="2"/>
-      <c r="D8" s="2" t="s">
-        <v>9</v>
+      <c r="D8" s="2">
+        <v>40</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
     </row>
-    <row r="9" spans="2:6" ht="21" customHeight="1">
+    <row r="9" spans="1:6" ht="21" customHeight="1">
       <c r="B9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C9" s="2"/>
-      <c r="D9" s="2" t="s">
-        <v>10</v>
+      <c r="D9" s="2">
+        <v>19</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
     </row>
-    <row r="10" spans="2:6" ht="21" customHeight="1">
+    <row r="10" spans="1:6" ht="21" customHeight="1">
       <c r="B10" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2"/>
-      <c r="D10" s="2" t="s">
-        <v>11</v>
+      <c r="D10" s="2">
+        <v>17</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
@@ -553,9 +611,328 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A3:G31"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="11.75" customWidth="1"/>
+    <col min="2" max="2" width="12.125" customWidth="1"/>
+    <col min="4" max="4" width="10.375" customWidth="1"/>
+    <col min="7" max="7" width="40.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:6">
+      <c r="B3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="36.75" customHeight="1">
+      <c r="A6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="2">
+        <v>1000</v>
+      </c>
+      <c r="F6" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="2">
+        <v>196</v>
+      </c>
+      <c r="D7" s="2">
+        <v>186</v>
+      </c>
+      <c r="E7" s="2">
+        <v>216</v>
+      </c>
+      <c r="F7" s="2">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="22.5" customHeight="1">
+      <c r="B8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2">
+        <v>78</v>
+      </c>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+    </row>
+    <row r="9" spans="1:6" ht="21" customHeight="1">
+      <c r="B9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2">
+        <v>35</v>
+      </c>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+    </row>
+    <row r="10" spans="1:6" ht="21" customHeight="1">
+      <c r="B10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2">
+        <v>45</v>
+      </c>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+    </row>
+    <row r="13" spans="1:6" ht="32.25" customHeight="1">
+      <c r="A13" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E13" s="2">
+        <v>1000</v>
+      </c>
+      <c r="F13" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="24" customHeight="1">
+      <c r="A14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" s="2">
+        <v>245</v>
+      </c>
+      <c r="D14" s="2">
+        <v>232</v>
+      </c>
+      <c r="E14" s="2">
+        <v>299</v>
+      </c>
+      <c r="F14" s="2">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="22.5" customHeight="1">
+      <c r="B15" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2">
+        <v>127</v>
+      </c>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+    </row>
+    <row r="16" spans="1:6" ht="23.25" customHeight="1">
+      <c r="B16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2">
+        <v>131</v>
+      </c>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+    </row>
+    <row r="17" spans="1:7" ht="22.5" customHeight="1">
+      <c r="B17" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2">
+        <v>87</v>
+      </c>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+    </row>
+    <row r="20" spans="1:7" ht="33.75" customHeight="1">
+      <c r="A20" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E20" s="2">
+        <v>1000</v>
+      </c>
+      <c r="F20" s="2">
+        <v>100</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="24" customHeight="1">
+      <c r="A21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C21" s="2">
+        <v>197</v>
+      </c>
+      <c r="D21" s="2">
+        <v>230</v>
+      </c>
+      <c r="E21" s="2">
+        <v>286</v>
+      </c>
+      <c r="F21" s="2">
+        <v>288</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="21.75" customHeight="1">
+      <c r="B22" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2">
+        <v>100</v>
+      </c>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+    </row>
+    <row r="23" spans="1:7" ht="23.25" customHeight="1">
+      <c r="B23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2">
+        <v>50</v>
+      </c>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+    </row>
+    <row r="24" spans="1:7" ht="19.5" customHeight="1">
+      <c r="B24" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2">
+        <v>41</v>
+      </c>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+    </row>
+    <row r="27" spans="1:7" ht="27">
+      <c r="A27" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E27" s="2">
+        <v>1000</v>
+      </c>
+      <c r="F27" s="2">
+        <v>100</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="23.25" customHeight="1">
+      <c r="A28" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="20.25" customHeight="1">
+      <c r="B29" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+    </row>
+    <row r="30" spans="1:7" ht="27" customHeight="1">
+      <c r="B30" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+    </row>
+    <row r="31" spans="1:7" ht="21.75" customHeight="1">
+      <c r="B31" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -563,10 +940,217 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A3:G20"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="12.75" customWidth="1"/>
+    <col min="2" max="2" width="15.125" customWidth="1"/>
+    <col min="4" max="4" width="10.375" customWidth="1"/>
+    <col min="7" max="7" width="32.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:7">
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="36.75" customHeight="1">
+      <c r="A7" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="2">
+        <v>1000</v>
+      </c>
+      <c r="F7" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="26.25" customHeight="1">
+      <c r="A8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" s="2">
+        <v>50</v>
+      </c>
+      <c r="D8" s="2">
+        <v>56</v>
+      </c>
+      <c r="E8" s="2">
+        <v>60</v>
+      </c>
+      <c r="F8" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="31.5" customHeight="1">
+      <c r="A11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="2">
+        <v>1000</v>
+      </c>
+      <c r="F11" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="25.5" customHeight="1">
+      <c r="A12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" s="2">
+        <v>178</v>
+      </c>
+      <c r="D12" s="2">
+        <v>169</v>
+      </c>
+      <c r="E12" s="2">
+        <v>176</v>
+      </c>
+      <c r="F12" s="2">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="13.5" customHeight="1">
+      <c r="A13" s="3"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+    </row>
+    <row r="15" spans="1:7" ht="36" customHeight="1">
+      <c r="A15" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E15" s="2">
+        <v>1000</v>
+      </c>
+      <c r="F15" s="2">
+        <v>100</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="24.75" customHeight="1">
+      <c r="A16" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="2">
+        <v>72</v>
+      </c>
+      <c r="D16" s="2">
+        <v>86</v>
+      </c>
+      <c r="E16" s="2">
+        <v>81</v>
+      </c>
+      <c r="F16" s="2">
+        <v>96</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="30" customHeight="1">
+      <c r="A19" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E19" s="2">
+        <v>1000</v>
+      </c>
+      <c r="F19" s="2">
+        <v>100</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="24.75" customHeight="1">
+      <c r="A20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/internal_doc/14.性能分析/sdbimport/bulkinsert.xlsx
+++ b/internal_doc/14.性能分析/sdbimport/bulkinsert.xlsx
@@ -151,7 +151,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -185,11 +185,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -206,6 +215,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -897,10 +910,18 @@
       <c r="B28" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
+      <c r="C28" s="2">
+        <v>187</v>
+      </c>
+      <c r="D28" s="2">
+        <v>223</v>
+      </c>
+      <c r="E28" s="2">
+        <v>269</v>
+      </c>
+      <c r="F28" s="2">
+        <v>302</v>
+      </c>
       <c r="G28" s="3" t="s">
         <v>25</v>
       </c>
@@ -910,7 +931,9 @@
         <v>5</v>
       </c>
       <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
+      <c r="D29" s="2">
+        <v>103</v>
+      </c>
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
     </row>
@@ -919,7 +942,9 @@
         <v>6</v>
       </c>
       <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
+      <c r="D30" s="2">
+        <v>65</v>
+      </c>
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
     </row>
@@ -940,7 +965,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A3:G20"/>
+  <dimension ref="A3:H20"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="12.75" customWidth="1"/>
@@ -949,7 +974,7 @@
     <col min="7" max="7" width="32.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:8">
       <c r="B3" t="s">
         <v>14</v>
       </c>
@@ -960,7 +985,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:8">
       <c r="B4" t="s">
         <v>15</v>
       </c>
@@ -971,12 +996,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:8">
       <c r="C5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="36.75" customHeight="1">
+    <row r="7" spans="1:8" ht="36.75" customHeight="1">
       <c r="A7" s="3" t="s">
         <v>20</v>
       </c>
@@ -996,7 +1021,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="26.25" customHeight="1">
+    <row r="8" spans="1:8" ht="26.25" customHeight="1">
       <c r="A8" s="3" t="s">
         <v>16</v>
       </c>
@@ -1016,7 +1041,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="31.5" customHeight="1">
+    <row r="11" spans="1:8" ht="31.5" customHeight="1">
       <c r="A11" s="3" t="s">
         <v>21</v>
       </c>
@@ -1036,7 +1061,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="25.5" customHeight="1">
+    <row r="12" spans="1:8" ht="25.5" customHeight="1">
       <c r="A12" s="3" t="s">
         <v>16</v>
       </c>
@@ -1056,7 +1081,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="13.5" customHeight="1">
+    <row r="13" spans="1:8" ht="13.5" customHeight="1">
       <c r="A13" s="3"/>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
@@ -1064,7 +1089,7 @@
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
     </row>
-    <row r="15" spans="1:7" ht="36" customHeight="1">
+    <row r="15" spans="1:8" ht="36" customHeight="1">
       <c r="A15" s="3" t="s">
         <v>22</v>
       </c>
@@ -1083,11 +1108,12 @@
       <c r="F15" s="2">
         <v>100</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" s="6" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" ht="24.75" customHeight="1">
+      <c r="H15" s="7"/>
+    </row>
+    <row r="16" spans="1:8" ht="24.75" customHeight="1">
       <c r="A16" s="3" t="s">
         <v>16</v>
       </c>
@@ -1110,7 +1136,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="30" customHeight="1">
+    <row r="19" spans="1:8" ht="30" customHeight="1">
       <c r="A19" s="3" t="s">
         <v>22</v>
       </c>
@@ -1129,21 +1155,30 @@
       <c r="F19" s="2">
         <v>100</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="G19" s="6" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" ht="24.75" customHeight="1">
+      <c r="H19" s="7"/>
+    </row>
+    <row r="20" spans="1:8" ht="24.75" customHeight="1">
       <c r="A20" s="3" t="s">
         <v>16</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
+      <c r="C20" s="2">
+        <v>59</v>
+      </c>
+      <c r="D20" s="2">
+        <v>69</v>
+      </c>
+      <c r="E20" s="2">
+        <v>83</v>
+      </c>
+      <c r="F20" s="2">
+        <v>89</v>
+      </c>
       <c r="G20" s="3" t="s">
         <v>25</v>
       </c>
